--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EC08BDC-B951-4BDC-B432-A8F549B55946}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52B2569F-8C7D-4F99-9E94-BC8633DCDBDC}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DF4116E-1E49-4906-96B9-DBC21578AF33}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE4DE6E6-5973-4575-A4F6-CB4AD0062AE7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FA3C9E-F13D-4CB2-A909-A9C56318D3EF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD684B88-DE7C-4BCD-89AE-859A87E1DD6B}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE4DE6E6-5973-4575-A4F6-CB4AD0062AE7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FA3C9E-F13D-4CB2-A909-A9C56318D3EF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD684B88-DE7C-4BCD-89AE-859A87E1DD6B}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB36D126-6791-4E21-9B46-115BD4C855C9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC386F02-045B-45DA-8EA1-062546F0DC8F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2593F519-D2D4-48CB-9C8A-7499E06051A2}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB36D126-6791-4E21-9B46-115BD4C855C9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC386F02-045B-45DA-8EA1-062546F0DC8F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2593F519-D2D4-48CB-9C8A-7499E06051A2}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{505A4E2D-1363-4F8A-91AA-641E62C6A475}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6967DCF-A791-4A68-ADAB-6E176456E0D3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6A9ABD-E19C-4BD6-861C-4500C4F67222}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{505A4E2D-1363-4F8A-91AA-641E62C6A475}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6967DCF-A791-4A68-ADAB-6E176456E0D3}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6A9ABD-E19C-4BD6-861C-4500C4F67222}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E106F74-A63D-4552-8B66-EC2BA833F288}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35A71F74-B2DB-4E25-A954-1E109A69F1BD}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EE78B1-0240-4D73-8B5D-D497104C20C5}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E106F74-A63D-4552-8B66-EC2BA833F288}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35A71F74-B2DB-4E25-A954-1E109A69F1BD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EE78B1-0240-4D73-8B5D-D497104C20C5}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9AC8747-FFA1-477F-9284-85E12EF0F0DE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09990AD0-F03F-4886-A7B8-F01B5F8A7083}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F74345B-BC95-4423-833D-8FC3219B4113}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9AC8747-FFA1-477F-9284-85E12EF0F0DE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09990AD0-F03F-4886-A7B8-F01B5F8A7083}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F74345B-BC95-4423-833D-8FC3219B4113}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69400234-B44C-4BCB-8EA9-0DBBB9B7044D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35C7E624-D448-44E1-A32E-39FE455B68FD}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F82C3F3D-4F10-4085-B8AE-AD78589CCAD7}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69400234-B44C-4BCB-8EA9-0DBBB9B7044D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35C7E624-D448-44E1-A32E-39FE455B68FD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F82C3F3D-4F10-4085-B8AE-AD78589CCAD7}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77411A98-B665-4D7B-94C0-02F16AA51D50}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C70F9A27-6056-4613-8C53-874D2D37C88F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5554EC1-F734-40BF-941A-D4DC90646277}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77411A98-B665-4D7B-94C0-02F16AA51D50}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C70F9A27-6056-4613-8C53-874D2D37C88F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5554EC1-F734-40BF-941A-D4DC90646277}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C4907B1-F75D-47D9-8F9B-A8590F006748}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C05B610A-81E8-4482-8744-34471924AAFE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AA8DD3E-1983-4B83-9896-93E6DE4B4483}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C4907B1-F75D-47D9-8F9B-A8590F006748}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C05B610A-81E8-4482-8744-34471924AAFE}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AA8DD3E-1983-4B83-9896-93E6DE4B4483}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,4 +2548,199 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
+    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E7D6E7-6A39-4FDF-82B7-BCAD9FD42269}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{997FA3DC-0B5A-4A4E-B144-A276DD67B11B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C10E808-583B-4548-98F6-40DF185CAD13}"/>
 </file>
--- a/Atana-ECC-KPI-Catalogue-v1.0.xlsx
+++ b/Atana-ECC-KPI-Catalogue-v1.0.xlsx
@@ -2548,199 +2548,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E3AE2BAD2C6FA4D8B4D95CE89FC31A3" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a2ce85c62cd7e9a608298e998330aeb7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1504f635df8bfa7d9525024d2d10bc95" ns2:_="">
-    <xsd:import namespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c4ac2493-9f1f-4345-86a0-c36146f38f1d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae81e17b-11c2-44ae-89e9-9ad5f5ff8880">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E7D6E7-6A39-4FDF-82B7-BCAD9FD42269}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{997FA3DC-0B5A-4A4E-B144-A276DD67B11B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C10E808-583B-4548-98F6-40DF185CAD13}"/>
 </file>